--- a/src/main/docs/Contribution Matrix.xlsx
+++ b/src/main/docs/Contribution Matrix.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBA79440-41C7-4B7E-8257-994D3BC44770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11745" yWindow="1965" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6720" yWindow="2385" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
